--- a/testcase/故障预警功能测试用例.xlsx
+++ b/testcase/故障预警功能测试用例.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O102"/>
+  <dimension ref="A1:O103"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -424,7 +424,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>测试对象:集控计费平台-故障预警(故障总览/故障详情/故障推送/故障代码库/顶部铃铛)  |  依据:《故障预警功能说明文档》V3.7(2026-09-11)</v>
+        <v>测试对象:集控计费平台-故障预警(故障总览/故障详情/故障推送/故障代码库/顶部铃铛)  |  依据:《故障预警功能说明文档》V3.8(2026-09-20)</v>
       </c>
     </row>
     <row r="3">
@@ -3016,7 +3016,7 @@
         <v>1. 核对表头、操作列与筛选栏</v>
       </c>
       <c r="K57" t="str">
-        <v>列=任务名称/启用(开关)/推送范围/推送方式/接收人/最近推送/操作(编辑·推送记录·删除);开启免打扰的实时任务推送方式列附免打扰时段标注;筛选栏=任务名称/启停状态/推送方式 + 搜索/重置 + 「故障代码库」按钮 + 「+新增推送任务」按钮。</v>
+        <v>列=任务名称/启用(开关)/推送范围/推送方式/接收人/最近推送/操作(编辑·推送记录·删除);开启免打扰的实时任务推送方式列附免打扰时段标注;推送范围列按类别分显(如 空调故障:故障/警示 · 项目运维:故障);筛选栏=任务名称/启停状态/推送方式 + 搜索/重置 + 「故障代码库」按钮与「+新增推送任务」按钮(两按钮相邻)。</v>
       </c>
       <c r="L57" t="str">
         <v>待测试</v>
@@ -3111,10 +3111,11 @@
       </c>
       <c r="J59" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 切换任意任务启停开关
-2. 对未配置接收人的任务开启</v>
+2. 对未配置接收人的任务开启
+3. 打开新增/编辑抽屉查看</v>
       </c>
       <c r="K59" t="str">
-        <v>开关即时生效并提示已启用/已停用;停用后该任务不再推送;未配置接收人的任务开启时提示先点「编辑」完善。</v>
+        <v>开关即时生效并提示已启用/已停用;停用后该任务不再推送;未配置接收人的任务开启时提示先点「编辑」完善;启停统一经该列开关控制——抽屉内无启用设置项,新建任务默认启用。</v>
       </c>
       <c r="L59" t="str">
         <v>待测试</v>
@@ -3259,7 +3260,7 @@
 2. 保存后再点该任务「编辑」</v>
       </c>
       <c r="K62" t="str">
-        <v>抽屉含:所属项目(只读,=当前项目)/任务名称(必填)/启用开关/推送范围(故障等级×故障类别勾选)/接收人/推送策略(推送方式+免打扰,免打扰仅实时推送可设定);无「故障持续时长」设置项(持续时长在故障代码库按故障码/故障类型配置,见代码库用例);编辑时各项回显与保存一致;底部仅取消/保存,无测试推送;无 24h 频控配置项,无内置去重、根因抑制等规则提示语(去重为后台内置规则,仅记录于文档 §7.3)。</v>
+        <v>抽屉含:任务名称(必填)/推送范围(空调故障与项目运维分别按故障等级勾选,某类不勾选=该类不推送)/接收人/推送策略(推送方式+免打扰,免打扰仅实时推送可设定);无「所属项目」展示(任务即当前项目,页面跟随右上角项目切换);无「启用」设置项(新建任务默认启用,启停统一经任务列表「启用」列开关控制);无「故障持续时长」设置项(持续时长在故障代码库按故障码/故障类型配置,见代码库用例);编辑时各项回显与保存一致;底部仅取消/保存,无测试推送;无 24h 频控配置项,无内置去重、根因抑制等规则提示语(去重为后台内置规则,仅记录于文档 §7.3)。</v>
       </c>
       <c r="L62" t="str">
         <v>待测试</v>
@@ -3335,7 +3336,7 @@
         <v>推送范围</v>
       </c>
       <c r="E64" t="str">
-        <v>范围勾选回显与保存校验</v>
+        <v>空调故障/项目运维等级分设与保存校验</v>
       </c>
       <c r="F64" t="str">
         <v>P0</v>
@@ -3347,16 +3348,16 @@
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
       <c r="I64" t="str">
-        <v>任务当前范围=故障×双类别</v>
+        <v>任务当前范围=两类各仅故障级</v>
       </c>
       <c r="J64" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 打开编辑核对范围勾选回显
-2. 增选「警示」保存,查看列表推送范围列
-3. 取消全部等级保存
-4. 取消全部类别保存</v>
+        <v xml:space="preserve">1. 打开编辑核对范围勾选回显(空调故障、项目运维各一组等级勾选)
+2. 空调故障增选「警示」保存,查看列表推送范围列
+3. 两类等级全部取消勾选后保存
+4. 仅保留项目运维一类等级保存</v>
       </c>
       <c r="K64" t="str">
-        <v>默认仅「故障」级+项目运维+空调故障;回显正确;保存后列表推送范围列同步更新;等级/类别任一为空时提示「推送范围需至少选择一个故障等级和一个故障类别」不放行;范围区注解:仅勾选范围内新产生的预警才会推送短信、项目屏蔽的故障不产生推送。</v>
+        <v>默认两类各仅「故障」级;回显正确;保存后列表推送范围列按类别分显同步更新;两类全不选时提示「推送范围需至少选择一个故障等级(空调故障或项目运维)」不放行;允许只给一类设等级(另一类不推送);范围区注解:仅勾选范围内新产生的预警才会推送短信、项目屏蔽的故障不产生推送。</v>
       </c>
       <c r="L64" t="str">
         <v>待测试</v>
@@ -3400,7 +3401,7 @@
         <v>无</v>
       </c>
       <c r="J65" t="str">
-        <v>1. 新增任务:启用开关打开、不添加接收人保存</v>
+        <v>1. 新增任务(默认启用):不添加接收人直接保存</v>
       </c>
       <c r="K65" t="str">
         <v>提示「已开启推送但未添加接收人,请先添加」不放行。</v>
@@ -3617,7 +3618,7 @@
         <v/>
       </c>
     </row>
-    <row r="70">
+    <row r="70" xml:space="preserve">
       <c r="A70">
         <v>66</v>
       </c>
@@ -3628,28 +3629,31 @@
         <v>推送-任务</v>
       </c>
       <c r="D70" t="str">
-        <v>接收人上限</v>
+        <v>手机号跨任务去重</v>
       </c>
       <c r="E70" t="str">
-        <v>单任务接收人上限 20</v>
+        <v>同一项目内一个手机号只允许存在于一个推送任务</v>
       </c>
       <c r="F70" t="str">
-        <v>P2</v>
+        <v>P0</v>
       </c>
       <c r="G70" t="str">
-        <v>边界</v>
+        <v>核心规则</v>
       </c>
       <c r="H70" t="str">
-        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。手机号 A 已配置在当前项目的任务甲接收人中。</v>
       </c>
       <c r="I70" t="str">
-        <v>第 21 个接收人</v>
-      </c>
-      <c r="J70" t="str">
-        <v>1. 添加至 20 人后再添加</v>
+        <v>手机号 A 加入任务乙 / 手机号 A 加入其他项目任务</v>
+      </c>
+      <c r="J70" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 编辑任务乙,从平台账号选择手机号 A 对应账号添加
+2. 手动录入手机号 A 点「发送验证码」
+3. 通过其他途径使任务乙含手机号 A 后点保存(兜底校验)
+4. 切换到另一项目的推送任务,添加手机号 A 并保存</v>
       </c>
       <c r="K70" t="str">
-        <v>提示达到上限,不允许添加。</v>
+        <v>① 平台账号添加即拦截,提示该手机号已在任务甲中配置(同一项目内一个手机号只允许存在于一个推送任务);② 手动录入在发送验证码前即拦截,不发送验证码;③ 保存兜底校验同样拦截并提示所在任务;④ 不同项目的推送任务允许使用同一手机号(去重仅按项目内判定)。</v>
       </c>
       <c r="L70" t="str">
         <v>待测试</v>
@@ -3661,10 +3665,10 @@
         <v/>
       </c>
       <c r="O70" t="str">
-        <v>默认上限 20 可后台调整(文档 §5.3)</v>
-      </c>
-    </row>
-    <row r="71" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
       <c r="A71">
         <v>67</v>
       </c>
@@ -3675,79 +3679,78 @@
         <v>推送-任务</v>
       </c>
       <c r="D71" t="str">
-        <v>推送策略</v>
+        <v>接收人上限</v>
       </c>
       <c r="E71" t="str">
-        <v>实时/每日汇总切换与免打扰联动</v>
+        <v>单任务接收人上限 20</v>
       </c>
       <c r="F71" t="str">
-        <v>P0</v>
+        <v>P2</v>
       </c>
       <c r="G71" t="str">
-        <v>功能</v>
+        <v>边界</v>
       </c>
       <c r="H71" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
       <c r="I71" t="str">
+        <v>第 21 个接收人</v>
+      </c>
+      <c r="J71" t="str">
+        <v>1. 添加至 20 人后再添加</v>
+      </c>
+      <c r="K71" t="str">
+        <v>提示达到上限,不允许添加。</v>
+      </c>
+      <c r="L71" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M71" t="str">
+        <v/>
+      </c>
+      <c r="N71" t="str">
+        <v/>
+      </c>
+      <c r="O71" t="str">
+        <v>默认上限 20 可后台调整(文档 §5.3)</v>
+      </c>
+    </row>
+    <row r="72" xml:space="preserve">
+      <c r="A72">
+        <v>68</v>
+      </c>
+      <c r="B72" t="str">
+        <v>ALM-068</v>
+      </c>
+      <c r="C72" t="str">
+        <v>推送-任务</v>
+      </c>
+      <c r="D72" t="str">
+        <v>推送策略</v>
+      </c>
+      <c r="E72" t="str">
+        <v>实时/每日汇总切换与免打扰联动</v>
+      </c>
+      <c r="F72" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G72" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H72" t="str">
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
+      </c>
+      <c r="I72" t="str">
         <v>每日 09:00</v>
       </c>
-      <c r="J71" t="str" xml:space="preserve">
+      <c r="J72" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 切换推送方式为每日汇总
 2. 观察免打扰设置与汇总时刻
 3. 设置时刻保存,查看列表推送方式列
 4. 切回实时推送保存</v>
       </c>
-      <c r="K71" t="str">
+      <c r="K72" t="str">
         <v>选每日汇总时显示时刻输入,且不展示免打扰时段设置(每日汇总无需设定免打扰,保存后免打扰不生效);保存后列表显示「每日汇总 09:00」;切回实时恢复展示免打扰设置,列表显示实时推送(开启免打扰时附时段标注)。</v>
-      </c>
-      <c r="L71" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M71" t="str">
-        <v/>
-      </c>
-      <c r="N71" t="str">
-        <v/>
-      </c>
-      <c r="O71" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="72" xml:space="preserve">
-      <c r="A72">
-        <v>68</v>
-      </c>
-      <c r="B72" t="str">
-        <v>ALM-068</v>
-      </c>
-      <c r="C72" t="str">
-        <v>推送-任务</v>
-      </c>
-      <c r="D72" t="str">
-        <v>免打扰</v>
-      </c>
-      <c r="E72" t="str">
-        <v>免打扰时段与故障级豁免注解</v>
-      </c>
-      <c r="F72" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G72" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H72" t="str">
-        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。(任务推送方式为实时推送)</v>
-      </c>
-      <c r="I72" t="str">
-        <v>22:00-08:00</v>
-      </c>
-      <c r="J72" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 开启免打扰
-2. 查看时段输入、豁免勾选与注解</v>
-      </c>
-      <c r="K72" t="str">
-        <v>免打扰时段仅实时推送方式下可设定(每日汇总无该设置);开启后显示起止时段+「故障级豁免」勾选(默认勾选);注解:免打扰时段内产生的预警不发送短信(时段结束后不补发),勾选豁免后故障级预警不受免打扰限制仍照常推送,豁免仅决定是否发送短信、平台内记录与统计不受影响;无「静音」表述。</v>
       </c>
       <c r="L72" t="str">
         <v>待测试</v>
@@ -3773,90 +3776,90 @@
         <v>推送-任务</v>
       </c>
       <c r="D73" t="str">
+        <v>免打扰</v>
+      </c>
+      <c r="E73" t="str">
+        <v>免打扰时段与故障级豁免注解</v>
+      </c>
+      <c r="F73" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G73" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H73" t="str">
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。(任务推送方式为实时推送)</v>
+      </c>
+      <c r="I73" t="str">
+        <v>22:00-08:00</v>
+      </c>
+      <c r="J73" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 开启免打扰
+2. 查看时段输入、豁免勾选与注解</v>
+      </c>
+      <c r="K73" t="str">
+        <v>免打扰时段仅实时推送方式下可设定(每日汇总无该设置);开启后显示起止时段+「故障级豁免」勾选(默认勾选);注解:免打扰时段内产生的预警不发送短信(时段结束后不补发),勾选豁免后故障级预警不受免打扰限制仍照常推送,豁免仅决定是否发送短信、平台内记录与统计不受影响;无「静音」表述。</v>
+      </c>
+      <c r="L73" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M73" t="str">
+        <v/>
+      </c>
+      <c r="N73" t="str">
+        <v/>
+      </c>
+      <c r="O73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74" xml:space="preserve">
+      <c r="A74">
+        <v>70</v>
+      </c>
+      <c r="B74" t="str">
+        <v>ALM-070</v>
+      </c>
+      <c r="C74" t="str">
+        <v>推送-任务</v>
+      </c>
+      <c r="D74" t="str">
         <v>内置去重</v>
       </c>
-      <c r="E73" t="str">
+      <c r="E74" t="str">
         <v>同一任务内同一对象同一故障仅首次推送(后端)</v>
       </c>
-      <c r="F73" t="str">
+      <c r="F74" t="str">
         <v>P0</v>
       </c>
-      <c r="G73" t="str">
+      <c r="G74" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H73" t="str">
+      <c r="H74" t="str">
         <v>平台具备上报模拟条件(或观察真实上报):同一对象同一故障持续期间重复上报。</v>
       </c>
-      <c r="I73" t="str">
+      <c r="I74" t="str">
         <v>重复上报 / 恢复后再发 / 处理后复发</v>
       </c>
-      <c r="J73" t="str" xml:space="preserve">
+      <c r="J74" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 故障持续期间重复上报,观察短信
 2. 故障恢复后再次发生,观察短信
 3. 处理闭环后同类故障复发,观察短信</v>
       </c>
-      <c r="K73" t="str">
+      <c r="K74" t="str">
         <v>① 同一任务内仅首次发生时推送一条,恢复前不重复推送;② 恢复后再次发生视为新故障,再次推送;③ 复发重新告警并可再次推送;去重按任务维度判定,不同任务间互不去重(见「多任务」用例);该规则后台默认执行,页面无配置项、无提示语。</v>
       </c>
-      <c r="L73" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M73" t="str">
-        <v/>
-      </c>
-      <c r="N73" t="str">
-        <v/>
-      </c>
-      <c r="O73" t="str">
+      <c r="L74" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M74" t="str">
+        <v/>
+      </c>
+      <c r="N74" t="str">
+        <v/>
+      </c>
+      <c r="O74" t="str">
         <v>规则详见文档 §7.3;替代原 24h 频控;根因抑制已移除(无此场景)</v>
-      </c>
-    </row>
-    <row r="74" xml:space="preserve">
-      <c r="A74">
-        <v>70</v>
-      </c>
-      <c r="B74" t="str">
-        <v>ALM-070</v>
-      </c>
-      <c r="C74" t="str">
-        <v>推送记录</v>
-      </c>
-      <c r="D74" t="str">
-        <v>打开与总量</v>
-      </c>
-      <c r="E74" t="str">
-        <v>按任务弹窗展示短信流水</v>
-      </c>
-      <c r="F74" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G74" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H74" t="str">
-        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
-      </c>
-      <c r="I74" t="str">
-        <v>任务存在短信推送记录</v>
-      </c>
-      <c r="J74" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 任务行点「推送记录」
-2. 再打开一个无推送记录的任务</v>
-      </c>
-      <c r="K74" t="str">
-        <v>弹窗标题含任务名;仅展示该任务的短信流水(无站内信记录、无根因合并记录),内容签名【空调集控】,按时间倒序;无记录的任务显示空态。</v>
-      </c>
-      <c r="L74" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M74" t="str">
-        <v/>
-      </c>
-      <c r="N74" t="str">
-        <v/>
-      </c>
-      <c r="O74" t="str">
-        <v/>
       </c>
     </row>
     <row r="75" xml:space="preserve">
@@ -3870,13 +3873,13 @@
         <v>推送记录</v>
       </c>
       <c r="D75" t="str">
-        <v>筛选</v>
+        <v>打开与总量</v>
       </c>
       <c r="E75" t="str">
-        <v>类型/状态/接收对象/时间筛选</v>
+        <v>按任务弹窗展示短信流水</v>
       </c>
       <c r="F75" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="G75" t="str">
         <v>功能</v>
@@ -3885,63 +3888,64 @@
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
       <c r="I75" t="str">
+        <v>任务存在短信推送记录</v>
+      </c>
+      <c r="J75" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 任务行点「推送记录」
+2. 再打开一个无推送记录的任务</v>
+      </c>
+      <c r="K75" t="str">
+        <v>弹窗标题含任务名;仅展示该任务的短信流水(无站内信记录、无根因合并记录),内容签名【空调集控】,按时间倒序;无记录的任务显示空态。</v>
+      </c>
+      <c r="L75" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M75" t="str">
+        <v/>
+      </c>
+      <c r="N75" t="str">
+        <v/>
+      </c>
+      <c r="O75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76" xml:space="preserve">
+      <c r="A76">
+        <v>72</v>
+      </c>
+      <c r="B76" t="str">
+        <v>ALM-072</v>
+      </c>
+      <c r="C76" t="str">
+        <v>推送记录</v>
+      </c>
+      <c r="D76" t="str">
+        <v>筛选</v>
+      </c>
+      <c r="E76" t="str">
+        <v>类型/状态/接收对象/时间筛选</v>
+      </c>
+      <c r="F76" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G76" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H76" t="str">
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
+      </c>
+      <c r="I76" t="str">
         <v>发送失败 / 接收人姓名</v>
       </c>
-      <c r="J75" t="str" xml:space="preserve">
+      <c r="J76" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 状态选发送失败查询
 2. 接收对象输入姓名/手机号查询
 3. 设置时间范围查询</v>
       </c>
-      <c r="K75" t="str">
+      <c r="K76" t="str">
         <v>① 仅命中发送失败记录(显红色);②③ 匹配过滤;状态仅含 发送中/已发送/发送失败(无已读/未读)。</v>
       </c>
-      <c r="L75" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M75" t="str">
-        <v/>
-      </c>
-      <c r="N75" t="str">
-        <v/>
-      </c>
-      <c r="O75" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76">
-        <v>72</v>
-      </c>
-      <c r="B76" t="str">
-        <v>ALM-072</v>
-      </c>
-      <c r="C76" t="str">
-        <v>故障代码库</v>
-      </c>
-      <c r="D76" t="str">
-        <v>弹窗标题</v>
-      </c>
-      <c r="E76" t="str">
-        <v>标题含当前项目+小字说明</v>
-      </c>
-      <c r="F76" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G76" t="str">
-        <v>界面</v>
-      </c>
-      <c r="H76" t="str">
-        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
-      </c>
-      <c r="I76" t="str">
-        <v>无</v>
-      </c>
-      <c r="J76" t="str">
-        <v>1. 点筛选栏「故障代码库」按钮</v>
-      </c>
-      <c r="K76" t="str">
-        <v>标题「故障代码库(当前项目:项目名)」,下方小字「配置仅对当前项目生效」;弹窗内页不再重复展示项目条;页签为「项目自定义」「项目屏蔽」「项目运维故障」。</v>
-      </c>
       <c r="L76" t="str">
         <v>待测试</v>
       </c>
@@ -3955,7 +3959,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" xml:space="preserve">
+    <row r="77">
       <c r="A77">
         <v>73</v>
       </c>
@@ -3966,10 +3970,10 @@
         <v>故障代码库</v>
       </c>
       <c r="D77" t="str">
-        <v>项目自定义</v>
+        <v>弹窗标题</v>
       </c>
       <c r="E77" t="str">
-        <v>表单含品牌/故障码/自定义等级/持续时长</v>
+        <v>标题含当前项目+小字说明</v>
       </c>
       <c r="F77" t="str">
         <v>P0</v>
@@ -3978,17 +3982,16 @@
         <v>界面</v>
       </c>
       <c r="H77" t="str">
-        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。打开代码库弹窗。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
       <c r="I77" t="str">
         <v>无</v>
       </c>
-      <c r="J77" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 项目自定义页签点「+添加自定义故障码」
-2. 核对表单与列表列</v>
+      <c r="J77" t="str">
+        <v>1. 点筛选栏「故障代码库」按钮</v>
       </c>
       <c r="K77" t="str">
-        <v>表单=空调品牌/故障代码/自定义等级/持续时长 四项(持续时长默认 0);无机型/名称/原因/排查方法输入(一律联查通用库);列表列=序号/品牌/故障代码/故障名称(通用库)/通用等级/本项目等级/持续时长/操作。</v>
+        <v>标题「故障代码库(当前项目:项目名)」,下方小字「配置仅对当前项目生效」;弹窗内页不再重复展示项目条;页签依次为「空调故障自定义」「空调故障屏蔽」「项目运维故障自定义」。</v>
       </c>
       <c r="L77" t="str">
         <v>待测试</v>
@@ -4014,16 +4017,16 @@
         <v>故障代码库</v>
       </c>
       <c r="D78" t="str">
-        <v>持续时长设置</v>
+        <v>空调故障自定义</v>
       </c>
       <c r="E78" t="str">
-        <v>自定义故障码持续时长回显与校验</v>
+        <v>表单含品牌/故障码/自定义等级/持续时长</v>
       </c>
       <c r="F78" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="G78" t="str">
-        <v>功能</v>
+        <v>界面</v>
       </c>
       <c r="H78" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。打开代码库弹窗。</v>
@@ -4032,11 +4035,11 @@
         <v>无</v>
       </c>
       <c r="J78" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 项目自定义添加/编辑某码,持续时长输入 10 保存,重新打开
-2. 分别输入负数、小数、非数字、置空尝试保存</v>
+        <v xml:space="preserve">1. 「空调故障自定义」页签点「+添加自定义故障码」
+2. 核对表单与列表列</v>
       </c>
       <c r="K78" t="str">
-        <v>保存后重新打开回显 10;负数/小数/非数字/置空均拦截并提示「持续时长需为不小于 0 的整数分钟」;默认 0=故障产生后立即推送;列表持续时长列同步显示(0 显示为立即推送)。</v>
+        <v>表单=空调品牌/故障代码/自定义等级/持续时长 四项(持续时长默认 0);无机型/名称/原因/排查方法输入(一律联查通用库);列表列=序号/品牌/故障代码/故障名称(通用库)/通用等级/本项目等级/持续时长/操作。</v>
       </c>
       <c r="L78" t="str">
         <v>待测试</v>
@@ -4062,78 +4065,78 @@
         <v>故障代码库</v>
       </c>
       <c r="D79" t="str">
+        <v>持续时长设置</v>
+      </c>
+      <c r="E79" t="str">
+        <v>自定义故障码持续时长回显与校验</v>
+      </c>
+      <c r="F79" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G79" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H79" t="str">
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。打开代码库弹窗。</v>
+      </c>
+      <c r="I79" t="str">
+        <v>无</v>
+      </c>
+      <c r="J79" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 「空调故障自定义」页签添加/编辑某码,持续时长输入 10 保存,重新打开
+2. 分别输入负数、小数、非数字、置空尝试保存</v>
+      </c>
+      <c r="K79" t="str">
+        <v>保存后重新打开回显 10;负数/小数/非数字/置空均拦截并提示「持续时长需为不小于 0 的整数分钟」;默认 0=故障产生后立即推送;列表持续时长列同步显示(0 显示为立即推送)。</v>
+      </c>
+      <c r="L79" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M79" t="str">
+        <v/>
+      </c>
+      <c r="N79" t="str">
+        <v/>
+      </c>
+      <c r="O79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80" xml:space="preserve">
+      <c r="A80">
+        <v>76</v>
+      </c>
+      <c r="B80" t="str">
+        <v>ALM-076</v>
+      </c>
+      <c r="C80" t="str">
+        <v>故障代码库</v>
+      </c>
+      <c r="D80" t="str">
         <v>持续时长生效</v>
       </c>
-      <c r="E79" t="str">
+      <c r="E80" t="str">
         <v>持续时长条件生效(实时推送)</v>
       </c>
-      <c r="F79" t="str">
+      <c r="F80" t="str">
         <v>P0</v>
       </c>
-      <c r="G79" t="str">
+      <c r="G80" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H79" t="str">
+      <c r="H80" t="str">
         <v>平台具备上报模拟条件:同一故障可控制产生与恢复;项目已将某故障码持续时长设为 10 分钟,且该码命中某实时推送任务范围。</v>
       </c>
-      <c r="I79" t="str">
-        <v>无</v>
-      </c>
-      <c r="J79" t="str" xml:space="preserve">
+      <c r="I80" t="str">
+        <v>无</v>
+      </c>
+      <c r="J80" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 制造该码故障后 10 分钟内恢复,观察短信与故障详情
 2. 制造故障持续满 10 分钟不恢复,观察短信
 3. 持续时长改回 0,再次制造故障,观察短信</v>
       </c>
-      <c r="K79" t="str">
+      <c r="K80" t="str">
         <v>① 时长内恢复的故障不推送短信(故障记录照常生成,持续时长不影响记录与统计);② 持续满 10 分钟仍未恢复的故障在满时长时点执行推送判断(任务范围、免打扰等)并发送;③ 持续时长为 0 时故障产生后立即执行推送判断。</v>
-      </c>
-      <c r="L79" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M79" t="str">
-        <v/>
-      </c>
-      <c r="N79" t="str">
-        <v/>
-      </c>
-      <c r="O79" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="80" xml:space="preserve">
-      <c r="A80">
-        <v>76</v>
-      </c>
-      <c r="B80" t="str">
-        <v>ALM-076</v>
-      </c>
-      <c r="C80" t="str">
-        <v>故障代码库</v>
-      </c>
-      <c r="D80" t="str">
-        <v>持续时长汇总</v>
-      </c>
-      <c r="E80" t="str">
-        <v>持续时长条件对每日汇总同样生效</v>
-      </c>
-      <c r="F80" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G80" t="str">
-        <v>核心规则</v>
-      </c>
-      <c r="H80" t="str">
-        <v>平台具备上报模拟条件:可控制故障产生与恢复时刻;项目已将某故障码持续时长设为 10 分钟,且该码命中某每日汇总任务范围。</v>
-      </c>
-      <c r="I80" t="str">
-        <v>无</v>
-      </c>
-      <c r="J80" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 前一自然日内制造两条该码故障:一条 10 分钟内恢复,一条持续满 10 分钟
-2. 到汇总时刻后观察汇总短信内容</v>
-      </c>
-      <c r="K80" t="str">
-        <v>每日汇总仅汇总持续满时长的故障预警:10 分钟内恢复的故障不计入汇总短信,持续满 10 分钟的故障计入。</v>
       </c>
       <c r="L80" t="str">
         <v>待测试</v>
@@ -4159,30 +4162,29 @@
         <v>故障代码库</v>
       </c>
       <c r="D81" t="str">
-        <v>运维故障页签</v>
+        <v>持续时长汇总</v>
       </c>
       <c r="E81" t="str">
-        <v>页签结构与行内编辑统一保存</v>
+        <v>持续时长条件对每日汇总同样生效</v>
       </c>
       <c r="F81" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="G81" t="str">
-        <v>界面</v>
+        <v>核心规则</v>
       </c>
       <c r="H81" t="str">
-        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。打开代码库弹窗,切到「项目运维故障」页签。</v>
+        <v>平台具备上报模拟条件:可控制故障产生与恢复时刻;项目已将某故障码持续时长设为 10 分钟,且该码命中某每日汇总任务范围。</v>
       </c>
       <c r="I81" t="str">
         <v>无</v>
       </c>
       <c r="J81" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 核对表格列与底部按钮
-2. 行内修改某类的本项目等级/持续时长,点「保存」
-3. 再做修改后点「取消」</v>
+        <v xml:space="preserve">1. 前一自然日内制造两条该码故障:一条 10 分钟内恢复,一条持续满 10 分钟
+2. 到汇总时刻后观察汇总短信内容</v>
       </c>
       <c r="K81" t="str">
-        <v>列=序号/故障名称/故障类别/默认等级/本项目等级(下拉)/持续时长(分钟)/屏蔽(开关);底部 取消/保存;保存后统一生效并提示「即时生效」;取消还原为已保存配置;默认等级列始终显示内置默认值;非计费项目不显示计费分摊类行。</v>
+        <v>每日汇总仅汇总持续满时长的故障预警:10 分钟内恢复的故障不计入汇总短信,持续满 10 分钟的故障计入。</v>
       </c>
       <c r="L81" t="str">
         <v>待测试</v>
@@ -4208,29 +4210,31 @@
         <v>故障代码库</v>
       </c>
       <c r="D82" t="str">
-        <v>运维等级</v>
+        <v>运维故障页签</v>
       </c>
       <c r="E82" t="str">
-        <v>运维故障等级自定义立即生效</v>
+        <v>页签结构与操作列按条保存/重置</v>
       </c>
       <c r="F82" t="str">
         <v>P0</v>
       </c>
       <c r="G82" t="str">
-        <v>核心规则</v>
+        <v>界面</v>
       </c>
       <c r="H82" t="str">
-        <v>平台存在某类项目运维故障的未处理记录。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。打开代码库弹窗,切到「项目运维故障自定义」页签。</v>
       </c>
       <c r="I82" t="str">
-        <v>电表离线:故障→警示</v>
+        <v>无</v>
       </c>
       <c r="J82" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 「项目运维故障」页签将「电表离线」本项目等级改为警示,保存
-2. 查看故障详情该类记录与等级统计</v>
+        <v xml:space="preserve">1. 核对表格列与操作列
+2. 行内修改某类的本项目等级/持续时长,点该行「保存」
+3. 再做修改后点该行「重置」
+4. 持续时长分别输入 -1、1441、1440 点该行「保存」</v>
       </c>
       <c r="K82" t="str">
-        <v>该类记录等级立即变为自定义等级(警示),铃铛/总览/详情等级统计联动;其他项目不受影响。</v>
+        <v>列=序号/故障名称/故障类别/默认等级/本项目等级(下拉)/持续时长(分钟)/屏蔽(开关)/操作(保存·重置);无底部整体保存/取消按钮;「保存」按条生效(仅该行,其他行未保存的改动不受影响)并提示即时生效;「重置」恢复该类默认等级与持续时长(0=立即推送)并立即生效,屏蔽状态不变;持续时长仅支持 0-1440 整数分钟(0=立即推送,最长 1 天):负数/小数/超上限(1441)保存拦截并提示,1440 边界可保存;默认等级列始终显示内置默认值;非计费项目不显示计费分摊类行。</v>
       </c>
       <c r="L82" t="str">
         <v>待测试</v>
@@ -4256,10 +4260,10 @@
         <v>故障代码库</v>
       </c>
       <c r="D83" t="str">
-        <v>运维屏蔽</v>
+        <v>运维等级</v>
       </c>
       <c r="E83" t="str">
-        <v>运维故障屏蔽二次确认并联动</v>
+        <v>运维故障等级自定义立即生效</v>
       </c>
       <c r="F83" t="str">
         <v>P0</v>
@@ -4271,16 +4275,14 @@
         <v>平台存在某类项目运维故障的未处理记录。</v>
       </c>
       <c r="I83" t="str">
-        <v>无</v>
+        <v>电表离线:故障→警示</v>
       </c>
       <c r="J83" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 打开该类的「屏蔽」开关,点「保存」
-2. 阅读二次确认文案后确认
-3. 查看故障详情/铃铛/总览
-4. 取消屏蔽再次保存</v>
+        <v xml:space="preserve">1. 「项目运维故障自定义」页签将「电表离线」本项目等级改为警示,点该行「保存」
+2. 查看故障详情该类记录与等级统计</v>
       </c>
       <c r="K83" t="str">
-        <v>二次确认说明:屏蔽后该类故障不再产生预警记录、计数与短信推送,历史记录同步不再展示;确认后该类记录从故障详情列表消失、计数联动减少、不再触发推送;取消屏蔽保存后恢复展示与计数。</v>
+        <v>该类记录等级立即变为自定义等级(警示),铃铛/总览/详情等级统计联动;其他项目不受影响。</v>
       </c>
       <c r="L83" t="str">
         <v>待测试</v>
@@ -4306,177 +4308,180 @@
         <v>故障代码库</v>
       </c>
       <c r="D84" t="str">
-        <v>运维持续时长</v>
+        <v>运维屏蔽</v>
       </c>
       <c r="E84" t="str">
-        <v>运维故障持续时长生效</v>
+        <v>运维故障屏蔽二次确认并联动</v>
       </c>
       <c r="F84" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="G84" t="str">
         <v>核心规则</v>
       </c>
       <c r="H84" t="str">
-        <v>平台具备上报模拟条件:可控制异常产生与消失时刻;项目已将某类运维故障持续时长设为 30 分钟,且该类命中某实时推送任务范围。</v>
+        <v>平台存在某类项目运维故障的未处理记录。</v>
       </c>
       <c r="I84" t="str">
         <v>无</v>
       </c>
       <c r="J84" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 打开该类的「屏蔽」开关,点该行「保存」
+2. 阅读二次确认文案后确认
+3. 查看故障详情/铃铛/总览
+4. 取消屏蔽后点该行「保存」</v>
+      </c>
+      <c r="K84" t="str">
+        <v>二次确认说明:屏蔽后该类故障不再产生预警记录、计数与短信推送,历史记录同步不再展示;确认后该类记录从故障详情列表消失、计数联动减少、不再触发推送;取消屏蔽保存后恢复展示与计数。</v>
+      </c>
+      <c r="L84" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M84" t="str">
+        <v/>
+      </c>
+      <c r="N84" t="str">
+        <v/>
+      </c>
+      <c r="O84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85" xml:space="preserve">
+      <c r="A85">
+        <v>81</v>
+      </c>
+      <c r="B85" t="str">
+        <v>ALM-081</v>
+      </c>
+      <c r="C85" t="str">
+        <v>故障代码库</v>
+      </c>
+      <c r="D85" t="str">
+        <v>运维持续时长</v>
+      </c>
+      <c r="E85" t="str">
+        <v>运维故障持续时长生效</v>
+      </c>
+      <c r="F85" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G85" t="str">
+        <v>核心规则</v>
+      </c>
+      <c r="H85" t="str">
+        <v>平台具备上报模拟条件:可控制异常产生与消失时刻;项目已将某类运维故障持续时长设为 30 分钟(允许范围 0-1440 整数,0=立即推送,最长 1 天),且该类命中某实时推送任务范围。</v>
+      </c>
+      <c r="I85" t="str">
+        <v>无</v>
+      </c>
+      <c r="J85" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 制造该类异常后 30 分钟内消失,观察短信
 2. 制造异常持续满 30 分钟不消失,观察短信
 3. 持续时长改回 0,再次制造异常</v>
       </c>
-      <c r="K84" t="str">
+      <c r="K85" t="str">
         <v>① 时长内消失的不推送;② 持续满 30 分钟仍未消失才触发推送;③ 0=产生后立即推送;持续时长不影响故障记录生成与统计。</v>
       </c>
-      <c r="L84" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M84" t="str">
-        <v/>
-      </c>
-      <c r="N84" t="str">
-        <v/>
-      </c>
-      <c r="O84" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="85" xml:space="preserve">
-      <c r="A85">
-        <v>81</v>
-      </c>
-      <c r="B85" t="str">
-        <v>ALM-081</v>
-      </c>
-      <c r="C85" t="str">
+      <c r="L85" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M85" t="str">
+        <v/>
+      </c>
+      <c r="N85" t="str">
+        <v/>
+      </c>
+      <c r="O85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86" xml:space="preserve">
+      <c r="A86">
+        <v>82</v>
+      </c>
+      <c r="B86" t="str">
+        <v>ALM-082</v>
+      </c>
+      <c r="C86" t="str">
         <v>故障代码库</v>
       </c>
-      <c r="D85" t="str">
-        <v>项目自定义</v>
-      </c>
-      <c r="E85" t="str">
+      <c r="D86" t="str">
+        <v>空调故障自定义</v>
+      </c>
+      <c r="E86" t="str">
         <v>通用库无此码时拒绝添加</v>
       </c>
-      <c r="F85" t="str">
+      <c r="F86" t="str">
         <v>P0</v>
       </c>
-      <c r="G85" t="str">
+      <c r="G86" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H85" t="str">
+      <c r="H86" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。打开代码库弹窗。</v>
       </c>
-      <c r="I85" t="str">
+      <c r="I86" t="str">
         <v>任一通用库未收录的品牌+故障码</v>
       </c>
-      <c r="J85" t="str" xml:space="preserve">
+      <c r="J86" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 添加自定义,输入未收录的品牌+代码
 2. 观察即时提示
 3. 点保存</v>
       </c>
-      <c r="K85" t="str">
+      <c r="K86" t="str">
         <v>即时提示:通用代码库无此故障码,无法自定义等级,如需监测请联系飞奕维护至通用故障码库;保存被拦截不放行;页面横幅同样注明未收录码走通用库维护(维护后自动纳入全部项目监测)。</v>
       </c>
-      <c r="L85" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M85" t="str">
-        <v/>
-      </c>
-      <c r="N85" t="str">
-        <v/>
-      </c>
-      <c r="O85" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="86" xml:space="preserve">
-      <c r="A86">
-        <v>82</v>
-      </c>
-      <c r="B86" t="str">
-        <v>ALM-082</v>
-      </c>
-      <c r="C86" t="str">
+      <c r="L86" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M86" t="str">
+        <v/>
+      </c>
+      <c r="N86" t="str">
+        <v/>
+      </c>
+      <c r="O86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87" xml:space="preserve">
+      <c r="A87">
+        <v>83</v>
+      </c>
+      <c r="B87" t="str">
+        <v>ALM-083</v>
+      </c>
+      <c r="C87" t="str">
         <v>故障代码库</v>
       </c>
-      <c r="D86" t="str">
-        <v>项目自定义</v>
-      </c>
-      <c r="E86" t="str">
+      <c r="D87" t="str">
+        <v>空调故障自定义</v>
+      </c>
+      <c r="E87" t="str">
         <v>等级自定义立即生效</v>
       </c>
-      <c r="F86" t="str">
+      <c r="F87" t="str">
         <v>P0</v>
       </c>
-      <c r="G86" t="str">
+      <c r="G87" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H86" t="str">
+      <c r="H87" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。打开代码库弹窗。</v>
       </c>
-      <c r="I86" t="str">
+      <c r="I87" t="str">
         <v>任一通用库已收录且存在故障记录的码</v>
       </c>
-      <c r="J86" t="str" xml:space="preserve">
+      <c r="J87" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 添加自定义输入该品牌+代码
 2. 观察提示与等级回显
 3. 将等级改为其他档保存
 4. 查看故障详情中该码记录</v>
       </c>
-      <c r="K86" t="str">
+      <c r="K87" t="str">
         <v>提示通用库已有该码及通用等级,回显默认=通用等级;保存后列表显示通用等级与本项目等级;该码故障记录等级立即变为自定义等级,统计联动。</v>
       </c>
-      <c r="L86" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M86" t="str">
-        <v/>
-      </c>
-      <c r="N86" t="str">
-        <v/>
-      </c>
-      <c r="O86" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87">
-        <v>83</v>
-      </c>
-      <c r="B87" t="str">
-        <v>ALM-083</v>
-      </c>
-      <c r="C87" t="str">
-        <v>故障代码库</v>
-      </c>
-      <c r="D87" t="str">
-        <v>项目自定义</v>
-      </c>
-      <c r="E87" t="str">
-        <v>删除后按通用等级生效</v>
-      </c>
-      <c r="F87" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G87" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H87" t="str">
-        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。项目已存在一条项目自定义配置,打开代码库弹窗。</v>
-      </c>
-      <c r="I87" t="str">
-        <v>无</v>
-      </c>
-      <c r="J87" t="str">
-        <v>1. 对该配置行点「删除」并确认</v>
-      </c>
-      <c r="K87" t="str">
-        <v>二次确认说明删除后按通用代码库等级生效;删除后清单移除该行,该码恢复按通用等级判定、持续时长恢复立即推送。</v>
-      </c>
       <c r="L87" t="str">
         <v>待测试</v>
       </c>
@@ -4490,7 +4495,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" xml:space="preserve">
+    <row r="88">
       <c r="A88">
         <v>84</v>
       </c>
@@ -4501,30 +4506,28 @@
         <v>故障代码库</v>
       </c>
       <c r="D88" t="str">
-        <v>大小写</v>
+        <v>空调故障自定义</v>
       </c>
       <c r="E88" t="str">
-        <v>小写码匹配与屏蔽生效</v>
+        <v>删除后按通用等级生效</v>
       </c>
       <c r="F88" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="G88" t="str">
-        <v>核心规则</v>
+        <v>功能</v>
       </c>
       <c r="H88" t="str">
-        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。打开代码库弹窗;项目存在小写故障码记录。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。项目已存在一条项目自定义配置,打开代码库弹窗。</v>
       </c>
       <c r="I88" t="str">
         <v>无</v>
       </c>
-      <c r="J88" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 项目屏蔽添加 该品牌/小写码
-2. 查看屏蔽清单联查信息
-3. 查看故障详情该码记录与统计</v>
+      <c r="J88" t="str">
+        <v>1. 对该配置行点「删除」并确认</v>
       </c>
       <c r="K88" t="str">
-        <v>屏蔽清单正确联查通用库名称与通用等级;该码记录不再出现在故障详情列表,计数联动减少;取消屏蔽恢复。</v>
+        <v>二次确认说明删除后按通用代码库等级生效;删除后清单移除该行,该码恢复按通用等级判定、持续时长恢复立即推送。</v>
       </c>
       <c r="L88" t="str">
         <v>待测试</v>
@@ -4553,7 +4556,7 @@
         <v>大小写</v>
       </c>
       <c r="E89" t="str">
-        <v>并存码严格区分与防呆</v>
+        <v>小写码匹配与屏蔽生效</v>
       </c>
       <c r="F89" t="str">
         <v>P0</v>
@@ -4562,165 +4565,166 @@
         <v>核心规则</v>
       </c>
       <c r="H89" t="str">
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。打开代码库弹窗;项目存在小写故障码记录。</v>
+      </c>
+      <c r="I89" t="str">
+        <v>无</v>
+      </c>
+      <c r="J89" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 「空调故障屏蔽」页签添加 该品牌/小写码
+2. 查看屏蔽清单联查信息
+3. 查看故障详情该码记录与统计</v>
+      </c>
+      <c r="K89" t="str">
+        <v>屏蔽清单正确联查通用库名称与通用等级;该码记录不再出现在故障详情列表,计数联动减少;取消屏蔽恢复。</v>
+      </c>
+      <c r="L89" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M89" t="str">
+        <v/>
+      </c>
+      <c r="N89" t="str">
+        <v/>
+      </c>
+      <c r="O89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90" xml:space="preserve">
+      <c r="A90">
+        <v>86</v>
+      </c>
+      <c r="B90" t="str">
+        <v>ALM-086</v>
+      </c>
+      <c r="C90" t="str">
+        <v>故障代码库</v>
+      </c>
+      <c r="D90" t="str">
+        <v>大小写</v>
+      </c>
+      <c r="E90" t="str">
+        <v>并存码严格区分与防呆</v>
+      </c>
+      <c r="F90" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G90" t="str">
+        <v>核心规则</v>
+      </c>
+      <c r="H90" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。打开代码库弹窗。</v>
       </c>
-      <c r="I89" t="str">
+      <c r="I90" t="str">
         <v>海信 EE(故障)/Ee(提示)</v>
       </c>
-      <c r="J89" t="str" xml:space="preserve">
+      <c r="J90" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 屏蔽 海信/Ee
 2. 验证 EE 等级不受影响
 3. 尝试输入 海信/ee 自定义或屏蔽</v>
       </c>
-      <c r="K89" t="str">
+      <c r="K90" t="str">
         <v>Ee 被屏蔽而 EE 判定仍为故障级;输入 ee(大小写歧义)时防呆提示存在并存码(EE/Ee),要求按设备上报大小写精确填写,不放行。</v>
       </c>
-      <c r="L89" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M89" t="str">
-        <v/>
-      </c>
-      <c r="N89" t="str">
-        <v/>
-      </c>
-      <c r="O89" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="90" xml:space="preserve">
-      <c r="A90">
-        <v>86</v>
-      </c>
-      <c r="B90" t="str">
-        <v>ALM-086</v>
-      </c>
-      <c r="C90" t="str">
+      <c r="L90" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M90" t="str">
+        <v/>
+      </c>
+      <c r="N90" t="str">
+        <v/>
+      </c>
+      <c r="O90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91" xml:space="preserve">
+      <c r="A91">
+        <v>87</v>
+      </c>
+      <c r="B91" t="str">
+        <v>ALM-087</v>
+      </c>
+      <c r="C91" t="str">
         <v>故障代码库</v>
       </c>
-      <c r="D90" t="str">
+      <c r="D91" t="str">
         <v>屏蔽联动</v>
       </c>
-      <c r="E90" t="str">
+      <c r="E91" t="str">
         <v>屏蔽即时联动计数与推送</v>
       </c>
-      <c r="F90" t="str">
+      <c r="F91" t="str">
         <v>P0</v>
       </c>
-      <c r="G90" t="str">
+      <c r="G91" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H90" t="str">
+      <c r="H91" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。打开代码库弹窗。</v>
       </c>
-      <c r="I90" t="str">
+      <c r="I91" t="str">
         <v>任一存在未处理记录的故障码</v>
       </c>
-      <c r="J90" t="str" xml:space="preserve">
+      <c r="J91" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 记录铃铛未处理总数
 2. 屏蔽该码
 3. 查看铃铛与总览
 4. 取消屏蔽</v>
       </c>
-      <c r="K90" t="str">
+      <c r="K91" t="str">
         <v>屏蔽后未处理总数按该码记录数减少(等级统计同步),该码不触发推送;取消后恢复;弹窗经遮罩关闭同样触发刷新。</v>
       </c>
-      <c r="L90" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M90" t="str">
-        <v/>
-      </c>
-      <c r="N90" t="str">
-        <v/>
-      </c>
-      <c r="O90" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="91" xml:space="preserve">
-      <c r="A91">
-        <v>87</v>
-      </c>
-      <c r="B91" t="str">
-        <v>ALM-087</v>
-      </c>
-      <c r="C91" t="str">
+      <c r="L91" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M91" t="str">
+        <v/>
+      </c>
+      <c r="N91" t="str">
+        <v/>
+      </c>
+      <c r="O91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92" xml:space="preserve">
+      <c r="A92">
+        <v>88</v>
+      </c>
+      <c r="B92" t="str">
+        <v>ALM-088</v>
+      </c>
+      <c r="C92" t="str">
         <v>故障代码库</v>
       </c>
-      <c r="D91" t="str">
+      <c r="D92" t="str">
         <v>互斥</v>
       </c>
-      <c r="E91" t="str">
+      <c r="E92" t="str">
         <v>屏蔽与项目自定义互斥需二次确认</v>
       </c>
-      <c r="F91" t="str">
+      <c r="F92" t="str">
         <v>P1</v>
       </c>
-      <c r="G91" t="str">
+      <c r="G92" t="str">
         <v>功能</v>
       </c>
-      <c r="H91" t="str">
+      <c r="H92" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。先对某码做项目自定义等级。</v>
       </c>
-      <c r="I91" t="str">
+      <c r="I92" t="str">
         <v>同码屏蔽</v>
       </c>
-      <c r="J91" t="str" xml:space="preserve">
+      <c r="J92" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 对该码添加屏蔽
 2. 阅读确认弹窗后确认
 3. 取消屏蔽后查看自定义清单</v>
       </c>
-      <c r="K91" t="str">
+      <c r="K92" t="str">
         <v>弹出二次确认(屏蔽将移除项目自定义等级配置,取消屏蔽后不自动恢复);确认后自定义清单中该码消失;取消屏蔽后按通用库等级生效,原自定义不恢复。</v>
-      </c>
-      <c r="L91" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M91" t="str">
-        <v/>
-      </c>
-      <c r="N91" t="str">
-        <v/>
-      </c>
-      <c r="O91" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="92" xml:space="preserve">
-      <c r="A92">
-        <v>88</v>
-      </c>
-      <c r="B92" t="str">
-        <v>ALM-088</v>
-      </c>
-      <c r="C92" t="str">
-        <v>故障代码库</v>
-      </c>
-      <c r="D92" t="str">
-        <v>项目隔离</v>
-      </c>
-      <c r="E92" t="str">
-        <v>代码库配置按项目隔离</v>
-      </c>
-      <c r="F92" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G92" t="str">
-        <v>核心规则</v>
-      </c>
-      <c r="H92" t="str">
-        <v>两个项目均存在同一故障码的记录。</v>
-      </c>
-      <c r="I92" t="str">
-        <v>项目A/项目B</v>
-      </c>
-      <c r="J92" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 在项目 A 代码库屏蔽该码
-2. 打开项目 B 代码库与故障详情</v>
-      </c>
-      <c r="K92" t="str">
-        <v>项目 B 的屏蔽清单不含该码,B 项目该码故障正常计数与展示。</v>
       </c>
       <c r="L92" t="str">
         <v>待测试</v>
@@ -4746,128 +4750,128 @@
         <v>故障代码库</v>
       </c>
       <c r="D93" t="str">
+        <v>项目隔离</v>
+      </c>
+      <c r="E93" t="str">
+        <v>代码库配置按项目隔离</v>
+      </c>
+      <c r="F93" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G93" t="str">
+        <v>核心规则</v>
+      </c>
+      <c r="H93" t="str">
+        <v>两个项目均存在同一故障码的记录。</v>
+      </c>
+      <c r="I93" t="str">
+        <v>项目A/项目B</v>
+      </c>
+      <c r="J93" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 在项目 A 代码库屏蔽该码
+2. 打开项目 B 代码库与故障详情</v>
+      </c>
+      <c r="K93" t="str">
+        <v>项目 B 的屏蔽清单不含该码,B 项目该码故障正常计数与展示。</v>
+      </c>
+      <c r="L93" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M93" t="str">
+        <v/>
+      </c>
+      <c r="N93" t="str">
+        <v/>
+      </c>
+      <c r="O93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94" xml:space="preserve">
+      <c r="A94">
+        <v>90</v>
+      </c>
+      <c r="B94" t="str">
+        <v>ALM-090</v>
+      </c>
+      <c r="C94" t="str">
+        <v>故障代码库</v>
+      </c>
+      <c r="D94" t="str">
         <v>重复校验</v>
       </c>
-      <c r="E93" t="str">
+      <c r="E94" t="str">
         <v>重复自定义/重复屏蔽拦截</v>
       </c>
-      <c r="F93" t="str">
+      <c r="F94" t="str">
         <v>P2</v>
       </c>
-      <c r="G93" t="str">
+      <c r="G94" t="str">
         <v>异常</v>
       </c>
-      <c r="H93" t="str">
+      <c r="H94" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。打开代码库弹窗。</v>
       </c>
-      <c r="I93" t="str">
-        <v>无</v>
-      </c>
-      <c r="J93" t="str" xml:space="preserve">
+      <c r="I94" t="str">
+        <v>无</v>
+      </c>
+      <c r="J94" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 对已有自定义配置的码再次添加
 2. 对已屏蔽的码再次屏蔽
 3. 对已屏蔽码执行自定义</v>
       </c>
-      <c r="K93" t="str">
+      <c r="K94" t="str">
         <v>分别提示:该故障码已有项目自定义配置/已在屏蔽清单中/在项目屏蔽清单中请先取消屏蔽。</v>
       </c>
-      <c r="L93" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M93" t="str">
-        <v/>
-      </c>
-      <c r="N93" t="str">
-        <v/>
-      </c>
-      <c r="O93" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="94" xml:space="preserve">
-      <c r="A94">
-        <v>90</v>
-      </c>
-      <c r="B94" t="str">
-        <v>ALM-090</v>
-      </c>
-      <c r="C94" t="str">
+      <c r="L94" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M94" t="str">
+        <v/>
+      </c>
+      <c r="N94" t="str">
+        <v/>
+      </c>
+      <c r="O94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95" xml:space="preserve">
+      <c r="A95">
+        <v>91</v>
+      </c>
+      <c r="B95" t="str">
+        <v>ALM-091</v>
+      </c>
+      <c r="C95" t="str">
         <v>非计费项目</v>
       </c>
-      <c r="D94" t="str">
+      <c r="D95" t="str">
         <v>全链路过滤</v>
       </c>
-      <c r="E94" t="str">
+      <c r="E95" t="str">
         <v>非计费项目隐藏计费分摊内容</v>
       </c>
-      <c r="F94" t="str">
+      <c r="F95" t="str">
         <v>P0</v>
       </c>
-      <c r="G94" t="str">
+      <c r="G95" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H94" t="str">
+      <c r="H95" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。切换到一个非计费项目(项目管理中未开启计费配置)。</v>
       </c>
-      <c r="I94" t="str">
-        <v>无</v>
-      </c>
-      <c r="J94" t="str" xml:space="preserve">
+      <c r="I95" t="str">
+        <v>无</v>
+      </c>
+      <c r="J95" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 查看铃铛计数
 2. 查看总览统计卡与饼图
 3. 查看故障详情子类下拉</v>
       </c>
-      <c r="K94" t="str">
+      <c r="K95" t="str">
         <v>所有计数不含计费分摊类(未处理=基础配置+空调故障);详情子类下拉仅「基础配置」;推送范围同样过滤。</v>
       </c>
-      <c r="L94" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M94" t="str">
-        <v/>
-      </c>
-      <c r="N94" t="str">
-        <v/>
-      </c>
-      <c r="O94" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="95" xml:space="preserve">
-      <c r="A95">
-        <v>91</v>
-      </c>
-      <c r="B95" t="str">
-        <v>ALM-091</v>
-      </c>
-      <c r="C95" t="str">
-        <v>深链</v>
-      </c>
-      <c r="D95" t="str">
-        <v>等级深链</v>
-      </c>
-      <c r="E95" t="str">
-        <v>level 深链双 Tab 同步</v>
-      </c>
-      <c r="F95" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G95" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H95" t="str">
-        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。</v>
-      </c>
-      <c r="I95" t="str">
-        <v>level=1 / level=3</v>
-      </c>
-      <c r="J95" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 直接访问 故障详情?level=1&amp;status=new
-2. 再访问 ?level=3&amp;status=new</v>
-      </c>
-      <c r="K95" t="str">
-        <v>level=1:两个 Tab 同步带入等级筛选,落地优先有数据的项目运维 Tab;level=3:项目运维该等级为 0 时直达空调故障 Tab。</v>
-      </c>
       <c r="L95" t="str">
         <v>待测试</v>
       </c>
@@ -4878,7 +4882,7 @@
         <v/>
       </c>
       <c r="O95" t="str">
-        <v>深链为页面直达能力(预留),当前统计卡/铃铛卡片均为纯展示不带跳转</v>
+        <v/>
       </c>
     </row>
     <row r="96" xml:space="preserve">
@@ -4892,10 +4896,10 @@
         <v>深链</v>
       </c>
       <c r="D96" t="str">
-        <v>today 深链</v>
+        <v>等级深链</v>
       </c>
       <c r="E96" t="str">
-        <v>今日新增深链当日范围+全部状态</v>
+        <v>level 深链双 Tab 同步</v>
       </c>
       <c r="F96" t="str">
         <v>P1</v>
@@ -4907,14 +4911,14 @@
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。</v>
       </c>
       <c r="I96" t="str">
-        <v>today=1</v>
+        <v>level=1 / level=3</v>
       </c>
       <c r="J96" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 直接访问 故障详情?today=1
-2. 查看两 Tab 筛选</v>
+        <v xml:space="preserve">1. 直接访问 故障详情?level=1&amp;status=new
+2. 再访问 ?level=3&amp;status=new</v>
       </c>
       <c r="K96" t="str">
-        <v>两 Tab 时间范围=当日、状态=全部;两 Tab 合计=当日新增数(空调 Tab 不含已屏蔽记录);落地优先有数据的项目运维。</v>
+        <v>level=1:两个 Tab 同步带入等级筛选,落地优先有数据的项目运维 Tab;level=3:项目运维该等级为 0 时直达空调故障 Tab。</v>
       </c>
       <c r="L96" t="str">
         <v>待测试</v>
@@ -4940,10 +4944,10 @@
         <v>深链</v>
       </c>
       <c r="D97" t="str">
-        <v>记录定位</v>
+        <v>today 深链</v>
       </c>
       <c r="E97" t="str">
-        <v>obj/addr 定位深链</v>
+        <v>今日新增深链当日范围+全部状态</v>
       </c>
       <c r="F97" t="str">
         <v>P1</v>
@@ -4955,61 +4959,62 @@
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。</v>
       </c>
       <c r="I97" t="str">
+        <v>today=1</v>
+      </c>
+      <c r="J97" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 直接访问 故障详情?today=1
+2. 查看两 Tab 筛选</v>
+      </c>
+      <c r="K97" t="str">
+        <v>两 Tab 时间范围=当日、状态=全部;两 Tab 合计=当日新增数(空调 Tab 不含已屏蔽记录);落地优先有数据的项目运维。</v>
+      </c>
+      <c r="L97" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M97" t="str">
+        <v/>
+      </c>
+      <c r="N97" t="str">
+        <v/>
+      </c>
+      <c r="O97" t="str">
+        <v>深链为页面直达能力(预留),当前统计卡/铃铛卡片均为纯展示不带跳转</v>
+      </c>
+    </row>
+    <row r="98" xml:space="preserve">
+      <c r="A98">
+        <v>94</v>
+      </c>
+      <c r="B98" t="str">
+        <v>ALM-094</v>
+      </c>
+      <c r="C98" t="str">
+        <v>深链</v>
+      </c>
+      <c r="D98" t="str">
+        <v>记录定位</v>
+      </c>
+      <c r="E98" t="str">
+        <v>obj/addr 定位深链</v>
+      </c>
+      <c r="F98" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G98" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H98" t="str">
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。</v>
+      </c>
+      <c r="I98" t="str">
         <v>任一运维/空调故障记录</v>
       </c>
-      <c r="J97" t="str" xml:space="preserve">
+      <c r="J98" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 总览最近故障点击一条运维记录
 2. 点击一条空调记录</v>
       </c>
-      <c r="K97" t="str">
+      <c r="K98" t="str">
         <v>运维:对象筛选自动填入、恰好定位该记录;空调:内机地址筛选填入、tab=ac 直达;状态=全部保证已处理记录可见。</v>
-      </c>
-      <c r="L97" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M97" t="str">
-        <v/>
-      </c>
-      <c r="N97" t="str">
-        <v/>
-      </c>
-      <c r="O97" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98">
-        <v>94</v>
-      </c>
-      <c r="B98" t="str">
-        <v>ALM-094</v>
-      </c>
-      <c r="C98" t="str">
-        <v>边界</v>
-      </c>
-      <c r="D98" t="str">
-        <v>配置兼容</v>
-      </c>
-      <c r="E98" t="str">
-        <v>旧版推送配置自动迁移</v>
-      </c>
-      <c r="F98" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G98" t="str">
-        <v>兼容</v>
-      </c>
-      <c r="H98" t="str">
-        <v>项目存在旧版本(单策略)结构的推送配置数据(功能迭代前配置)。</v>
-      </c>
-      <c r="I98" t="str">
-        <v>无</v>
-      </c>
-      <c r="J98" t="str">
-        <v>1. 打开故障推送页</v>
-      </c>
-      <c r="K98" t="str">
-        <v>旧版单策略配置自动迁移为一套推送任务(名称「默认推送任务」,推送范围/接收人/推送方式/免打扰保留),页面正常渲染无报错;旧版策略级「故障持续时长」配置废弃不再生效(改在故障代码库按故障码/故障类型配置)。</v>
       </c>
       <c r="L98" t="str">
         <v>待测试</v>
@@ -5035,28 +5040,28 @@
         <v>边界</v>
       </c>
       <c r="D99" t="str">
-        <v>树楼栋校验</v>
+        <v>配置兼容</v>
       </c>
       <c r="E99" t="str">
-        <v>多楼栋不串层</v>
+        <v>旧版推送配置自动迁移</v>
       </c>
       <c r="F99" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="G99" t="str">
-        <v>边界</v>
+        <v>兼容</v>
       </c>
       <c r="H99" t="str">
-        <v>项目含多楼栋且各楼栋有同名楼层。</v>
+        <v>项目存在旧版本(单策略,或范围结构为 故障等级×故障类别)的推送配置数据(功能迭代前配置)。</v>
       </c>
       <c r="I99" t="str">
         <v>无</v>
       </c>
       <c r="J99" t="str">
-        <v>1. 建筑树选「某楼栋-某层」</v>
+        <v>1. 打开故障推送页</v>
       </c>
       <c r="K99" t="str">
-        <v>仅命中该楼栋该层记录,不含其他楼栋同名楼层。</v>
+        <v>旧版单策略配置自动迁移为一套推送任务(名称「默认推送任务」,推送范围/接收人/推送方式/免打扰保留),页面正常渲染无报错;旧版「等级×类别」范围结构自动迁移为分类等级(被勾选的类别继承原等级集合,未勾选类别=不推送);旧版策略级「故障持续时长」配置废弃不再生效(改在故障代码库按故障码/故障类型配置)。</v>
       </c>
       <c r="L99" t="str">
         <v>待测试</v>
@@ -5082,10 +5087,10 @@
         <v>边界</v>
       </c>
       <c r="D100" t="str">
-        <v>空态</v>
+        <v>树楼栋校验</v>
       </c>
       <c r="E100" t="str">
-        <v>筛选无结果与空数据展示</v>
+        <v>多楼栋不串层</v>
       </c>
       <c r="F100" t="str">
         <v>P2</v>
@@ -5094,16 +5099,16 @@
         <v>边界</v>
       </c>
       <c r="H100" t="str">
-        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。</v>
+        <v>项目含多楼栋且各楼栋有同名楼层。</v>
       </c>
       <c r="I100" t="str">
-        <v>不存在的关键字 XXXX</v>
+        <v>无</v>
       </c>
       <c r="J100" t="str">
-        <v>1. 对象输入 XXXX 查询</v>
+        <v>1. 建筑树选「某楼栋-某层」</v>
       </c>
       <c r="K100" t="str">
-        <v>列表显示空态占位(暂无数据)。</v>
+        <v>仅命中该楼栋该层记录,不含其他楼栋同名楼层。</v>
       </c>
       <c r="L100" t="str">
         <v>待测试</v>
@@ -5118,7 +5123,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" xml:space="preserve">
+    <row r="101">
       <c r="A101">
         <v>97</v>
       </c>
@@ -5129,29 +5134,28 @@
         <v>边界</v>
       </c>
       <c r="D101" t="str">
-        <v>输入转义</v>
+        <v>空态</v>
       </c>
       <c r="E101" t="str">
-        <v>特殊字符输入不破坏页面</v>
+        <v>筛选无结果与空数据展示</v>
       </c>
       <c r="F101" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="G101" t="str">
-        <v>安全</v>
+        <v>边界</v>
       </c>
       <c r="H101" t="str">
-        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I101" t="str">
-        <v>备注/姓名含 " ' &lt;script&gt;</v>
-      </c>
-      <c r="J101" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 处理备注、接收人姓名输入含引号与脚本标签
-2. 保存后查看列表与详情</v>
+        <v>不存在的关键字 XXXX</v>
+      </c>
+      <c r="J101" t="str">
+        <v>1. 对象输入 XXXX 查询</v>
       </c>
       <c r="K101" t="str">
-        <v>内容按纯文本转义展示,不执行脚本、不破坏按钮与布局。</v>
+        <v>列表显示空态占位(暂无数据)。</v>
       </c>
       <c r="L101" t="str">
         <v>待测试</v>
@@ -5163,7 +5167,7 @@
         <v/>
       </c>
       <c r="O101" t="str">
-        <v>开发侧统一 HTML 转义要求(文档 §六 实现约束)</v>
+        <v/>
       </c>
     </row>
     <row r="102" xml:space="preserve">
@@ -5177,46 +5181,94 @@
         <v>边界</v>
       </c>
       <c r="D102" t="str">
-        <v>状态持久</v>
+        <v>输入转义</v>
       </c>
       <c r="E102" t="str">
-        <v>刷新后处理状态与配置保留</v>
+        <v>特殊字符输入不破坏页面</v>
       </c>
       <c r="F102" t="str">
         <v>P1</v>
       </c>
       <c r="G102" t="str">
+        <v>安全</v>
+      </c>
+      <c r="H102" t="str">
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。</v>
+      </c>
+      <c r="I102" t="str">
+        <v>备注/姓名含 " ' &lt;script&gt;</v>
+      </c>
+      <c r="J102" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 处理备注、接收人姓名输入含引号与脚本标签
+2. 保存后查看列表与详情</v>
+      </c>
+      <c r="K102" t="str">
+        <v>内容按纯文本转义展示,不执行脚本、不破坏按钮与布局。</v>
+      </c>
+      <c r="L102" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M102" t="str">
+        <v/>
+      </c>
+      <c r="N102" t="str">
+        <v/>
+      </c>
+      <c r="O102" t="str">
+        <v>开发侧统一 HTML 转义要求(文档 §六 实现约束)</v>
+      </c>
+    </row>
+    <row r="103" xml:space="preserve">
+      <c r="A103">
+        <v>99</v>
+      </c>
+      <c r="B103" t="str">
+        <v>ALM-099</v>
+      </c>
+      <c r="C103" t="str">
+        <v>边界</v>
+      </c>
+      <c r="D103" t="str">
+        <v>状态持久</v>
+      </c>
+      <c r="E103" t="str">
+        <v>刷新后处理状态与配置保留</v>
+      </c>
+      <c r="F103" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G103" t="str">
         <v>功能</v>
       </c>
-      <c r="H102" t="str">
+      <c r="H103" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。处理/忽略若干记录,配置屏蔽码与项目自定义等级。</v>
       </c>
-      <c r="I102" t="str">
-        <v>无</v>
-      </c>
-      <c r="J102" t="str" xml:space="preserve">
+      <c r="I103" t="str">
+        <v>无</v>
+      </c>
+      <c r="J103" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 刷新页面或重新登录
 2. 逐项核对</v>
       </c>
-      <c r="K102" t="str">
+      <c r="K103" t="str">
         <v>处理状态、忽略、屏蔽清单、项目自定义、推送配置均保留;计数一致。</v>
       </c>
-      <c r="L102" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M102" t="str">
-        <v/>
-      </c>
-      <c r="N102" t="str">
-        <v/>
-      </c>
-      <c r="O102" t="str">
+      <c r="L103" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M103" t="str">
+        <v/>
+      </c>
+      <c r="N103" t="str">
+        <v/>
+      </c>
+      <c r="O103" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O102"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O103"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5256,7 +5308,7 @@
         <v>设计依据</v>
       </c>
       <c r="B5" t="str">
-        <v>《故障预警功能说明文档》V3.7(2026-09-11);判定规则与默认阈值见文档 §七</v>
+        <v>《故障预警功能说明文档》V3.8(2026-09-20);判定规则与默认阈值见文档 §七</v>
       </c>
     </row>
     <row r="6">
@@ -5272,7 +5324,7 @@
         <v>用例总数</v>
       </c>
       <c r="B7">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8">
@@ -5395,10 +5447,10 @@
         <v>推送-任务</v>
       </c>
       <c r="B20">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C20" t="str">
-        <v>多任务并行分别推送、抽屉(名称/开关/范围/接收人/策略)、校验、铃铛不受限、手动手机号短信验证码验证、免打扰豁免注解、内置去重(按任务,后台规则)</v>
+        <v>多任务并行分别推送、抽屉(名称/开关/范围(空调故障/项目运维分设等级)/接收人/策略)、校验、手机号跨任务去重(同项目唯一)、铃铛不受限、手动手机号短信验证码验证、免打扰豁免注解、内置去重(按任务,后台规则)</v>
       </c>
     </row>
     <row r="21">
@@ -5420,7 +5472,7 @@
         <v>18</v>
       </c>
       <c r="C22" t="str">
-        <v>项目自定义(等级+持续时长、未收录码拦截、立即生效、删除恢复)、持续时长(设置/实时生效/每日汇总生效)、项目运维故障页签(等级/持续时长/屏蔽,行内编辑统一保存)、大小写与并存码、屏蔽联动与互斥、项目隔离</v>
+        <v>空调故障自定义(等级+持续时长、未收录码拦截、立即生效、删除恢复)、持续时长(设置/实时生效/每日汇总生效)、项目运维故障自定义页签(等级/持续时长/屏蔽,操作列按条保存/重置)、大小写与并存码、屏蔽联动与互斥、项目隔离</v>
       </c>
     </row>
     <row r="23">
